--- a/electronica/electronica_Aussteller_Ampel.xlsx
+++ b/electronica/electronica_Aussteller_Ampel.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hinweise" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'electronica 2026'!$A$1:$L$616</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'electronica 2026'!$A$1:$M$616</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L616"/>
+  <dimension ref="A1:M616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -561,6 +562,11 @@
           <t>Stichprobe Jey</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Jey-Regel (22.10.)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -621,6 +627,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -681,6 +688,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -741,6 +749,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -801,6 +810,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -861,6 +871,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -921,6 +932,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -981,6 +993,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1041,6 +1058,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1101,6 +1123,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1161,6 +1184,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1221,6 +1249,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1281,6 +1310,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1341,6 +1375,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1401,6 +1436,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1461,6 +1497,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1521,6 +1558,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1581,6 +1619,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1641,6 +1680,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1701,6 +1741,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1761,6 +1806,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1817,6 +1863,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1877,6 +1924,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1937,6 +1985,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1997,6 +2050,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2057,6 +2111,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2117,6 +2172,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2177,6 +2233,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2237,6 +2294,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2297,6 +2355,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2357,6 +2416,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2417,6 +2481,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2477,6 +2542,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2537,6 +2603,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2597,6 +2664,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2657,6 +2729,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2717,6 +2790,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2777,6 +2851,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2837,6 +2912,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2897,6 +2973,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2957,6 +3034,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3017,6 +3095,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3077,6 +3160,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3137,6 +3221,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3197,6 +3282,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -3253,6 +3339,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -3313,6 +3400,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -3373,6 +3461,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3433,6 +3526,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -3493,6 +3587,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3553,6 +3648,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3613,6 +3709,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3673,6 +3770,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3733,6 +3831,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3793,6 +3892,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3853,6 +3953,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3913,6 +4018,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3973,6 +4083,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -4033,6 +4148,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -4089,6 +4205,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -4149,6 +4270,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -4209,6 +4335,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -4269,6 +4396,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -4329,6 +4457,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -4389,6 +4518,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -4449,6 +4583,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -4509,6 +4648,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -4569,6 +4713,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -4629,6 +4774,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -4689,6 +4835,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -4749,6 +4896,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -4809,6 +4957,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -4869,6 +5018,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -4929,6 +5079,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -4989,6 +5140,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -5049,6 +5201,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -5109,6 +5266,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -5169,6 +5327,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -5229,6 +5388,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -5289,6 +5449,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -5349,6 +5510,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -5409,6 +5571,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -5469,6 +5632,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -5529,6 +5693,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -5589,6 +5754,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -5649,6 +5815,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -5709,6 +5876,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -5769,6 +5937,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -5829,6 +5998,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -5889,6 +6059,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -5949,6 +6120,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -6009,6 +6181,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -6069,6 +6242,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -6129,6 +6307,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -6189,6 +6368,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -6249,6 +6429,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -6309,6 +6494,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -6369,6 +6559,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -6429,6 +6620,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -6489,6 +6681,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -6549,6 +6742,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -6609,6 +6807,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -6669,6 +6868,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -6729,6 +6929,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -6789,6 +6990,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -6849,6 +7055,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -6909,6 +7116,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -6969,6 +7177,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -7029,6 +7242,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -7089,6 +7303,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -7149,6 +7364,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -7209,6 +7425,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -7269,6 +7486,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -7329,6 +7547,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -7389,6 +7608,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -7449,6 +7669,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -7509,6 +7730,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -7569,6 +7791,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -7629,6 +7852,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -7689,6 +7913,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -7749,6 +7974,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -7809,6 +8035,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -7869,6 +8096,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -7929,6 +8157,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -7989,6 +8218,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -8049,6 +8279,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -8109,6 +8340,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -8169,6 +8405,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -8229,6 +8466,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -8289,6 +8527,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -8349,6 +8588,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -8409,6 +8653,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -8465,6 +8710,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -8525,6 +8771,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -8581,6 +8828,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -8637,6 +8885,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -8693,6 +8942,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -8753,6 +9007,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -8813,6 +9072,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -8869,6 +9133,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -8925,6 +9194,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -8981,6 +9251,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -9037,6 +9308,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -9097,6 +9369,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -9153,6 +9426,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -9209,6 +9483,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -9269,6 +9544,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -9329,6 +9605,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -9389,6 +9666,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -9449,6 +9727,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -9509,6 +9788,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -9569,6 +9849,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -9629,6 +9910,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -9689,6 +9971,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -9749,6 +10032,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -9809,6 +10093,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -9869,6 +10154,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -9929,6 +10215,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -9989,6 +10276,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -10049,6 +10337,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -10109,6 +10398,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -10169,6 +10459,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -10229,6 +10520,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -10289,6 +10581,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -10349,6 +10642,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -10409,6 +10703,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -10469,6 +10768,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -10529,6 +10829,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -10589,6 +10890,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -10649,6 +10951,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -10709,6 +11012,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -10769,6 +11073,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -10829,6 +11134,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -10889,6 +11195,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -10949,6 +11256,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -11009,6 +11317,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -11069,6 +11378,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -11129,6 +11439,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -11189,6 +11504,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -11249,6 +11565,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -11309,6 +11630,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -11369,6 +11691,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -11429,6 +11756,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -11489,6 +11817,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -11549,6 +11882,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -11609,6 +11943,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -11669,6 +12004,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -11729,6 +12065,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -11789,6 +12126,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -11849,6 +12187,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -11909,6 +12248,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -11969,6 +12309,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -12029,6 +12370,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -12089,6 +12431,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -12149,6 +12492,7 @@
           <t>ja (Rot-Kandidat E2/E3)</t>
         </is>
       </c>
+      <c r="M195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -12209,6 +12553,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -12269,6 +12614,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -12329,6 +12675,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -12389,6 +12736,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -12449,6 +12797,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -12509,6 +12862,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -12569,6 +12923,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -12629,6 +12984,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -12689,6 +13045,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -12749,6 +13106,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -12809,6 +13167,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -12869,6 +13228,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -12929,6 +13289,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -12989,6 +13350,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -13049,6 +13411,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -13109,6 +13472,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -13169,6 +13533,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -13229,6 +13594,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -13289,6 +13655,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -13349,6 +13720,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -13409,6 +13785,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -13469,6 +13846,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -13529,6 +13907,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -13589,6 +13968,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -13649,6 +14029,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -13709,6 +14090,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -13769,6 +14151,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -13829,6 +14212,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -13889,6 +14273,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -13949,6 +14334,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -14009,6 +14395,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -14069,6 +14456,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -14129,6 +14521,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -14189,6 +14582,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -14249,6 +14643,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -14309,6 +14704,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -14369,6 +14765,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -14429,6 +14826,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -14489,6 +14887,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -14549,6 +14948,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -14609,6 +15009,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -14669,6 +15074,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -14729,6 +15135,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -14789,6 +15200,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -14849,6 +15261,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -14909,6 +15322,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -14969,6 +15387,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -15029,6 +15452,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -15089,6 +15517,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -15149,6 +15582,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -15209,6 +15647,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -15269,6 +15712,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -15329,6 +15777,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -15389,6 +15838,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -15449,6 +15899,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -15509,6 +15960,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -15569,6 +16021,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -15629,6 +16082,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -15689,6 +16143,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -15749,6 +16204,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -15809,6 +16265,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -15869,6 +16326,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -15929,6 +16387,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -15989,6 +16448,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -16049,6 +16509,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -16109,6 +16570,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -16169,6 +16631,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -16229,6 +16696,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -16289,6 +16757,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -16349,6 +16818,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -16409,6 +16879,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -16469,6 +16940,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -16529,6 +17001,7 @@
           <t>ja (Rot-Kandidat E3)</t>
         </is>
       </c>
+      <c r="M268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -16589,6 +17062,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -16649,6 +17127,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -16709,6 +17188,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -16769,6 +17249,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -16829,6 +17310,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -16889,6 +17371,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -16949,6 +17432,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M275" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -17009,6 +17497,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -17069,6 +17558,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M277" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -17129,6 +17623,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -17189,6 +17688,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M279" s="2" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -17249,6 +17749,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -17309,6 +17810,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M281" s="2" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -17369,6 +17871,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -17429,6 +17932,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -17489,6 +17993,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -17549,6 +18054,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -17609,6 +18115,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -17669,6 +18176,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M287" s="2" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -17729,6 +18237,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -17789,6 +18298,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M289" s="2" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -17849,6 +18359,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -17909,6 +18420,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M291" s="2" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -17969,6 +18481,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -18029,6 +18542,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -18089,6 +18603,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -18149,6 +18664,11 @@
           <t>nein (Rot-Kandidat E2, nachrangig)</t>
         </is>
       </c>
+      <c r="M295" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -18209,6 +18729,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -18269,6 +18790,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M297" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -18329,6 +18855,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -18389,6 +18916,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M299" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -18449,6 +18981,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M300" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -18509,6 +19046,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M301" s="2" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -18569,6 +19107,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -18629,6 +19168,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M303" s="2" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -18689,6 +19229,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -18749,6 +19290,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -18809,6 +19351,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -18869,6 +19412,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M307" s="2" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -18929,6 +19473,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -18989,6 +19534,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M309" s="2" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -19049,6 +19595,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -19109,6 +19656,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M311" s="2" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -19169,6 +19717,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -19229,6 +19778,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -19289,6 +19839,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -19349,6 +19900,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -19409,6 +19961,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M316" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -19469,6 +20026,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M317" s="2" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -19529,6 +20087,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -19589,6 +20148,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M319" s="2" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -19649,6 +20209,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M320" s="2" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -19709,6 +20270,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M321" s="2" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -19769,6 +20331,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -19829,6 +20392,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M323" s="2" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -19889,6 +20453,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -19949,6 +20514,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M325" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -20009,6 +20579,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -20069,6 +20640,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M327" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -20129,6 +20705,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M328" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -20189,6 +20770,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M329" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -20249,6 +20835,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M330" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -20309,6 +20900,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M331" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -20369,6 +20965,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -20429,6 +21026,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M333" s="2" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -20489,6 +21087,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M334" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -20549,6 +21152,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M335" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -20609,6 +21217,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M336" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -20669,6 +21282,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M337" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -20729,6 +21347,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M338" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -20789,6 +21412,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M339" s="2" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -20849,6 +21473,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -20909,6 +21534,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M341" s="2" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -20969,6 +21595,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M342" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -21029,6 +21660,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M343" s="2" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -21089,6 +21721,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M344" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -21149,6 +21786,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M345" s="2" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -21209,6 +21847,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M346" s="2" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -21269,6 +21908,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M347" s="2" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -21329,6 +21969,7 @@
           <t>ja (Rot-Kandidat E2/E1)</t>
         </is>
       </c>
+      <c r="M348" s="2" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -21389,6 +22030,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M349" s="2" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -21449,6 +22091,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -21509,6 +22152,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M351" s="2" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -21569,6 +22213,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -21629,6 +22274,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M353" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -21689,6 +22339,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -21749,6 +22400,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -21809,6 +22461,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -21869,6 +22522,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M357" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -21929,6 +22587,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M358" s="2" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
@@ -21989,6 +22648,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M359" s="2" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -22049,6 +22709,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -22109,6 +22770,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M361" s="2" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -22169,6 +22831,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M362" s="2" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -22229,6 +22892,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M363" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
@@ -22289,6 +22957,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -22349,6 +23018,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M365" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -22409,6 +23083,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
@@ -22469,6 +23144,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M367" s="2" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
@@ -22529,6 +23205,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
@@ -22589,6 +23266,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M369" s="2" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
@@ -22649,6 +23327,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M370" s="2" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
@@ -22709,6 +23388,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M371" s="2" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
@@ -22769,6 +23449,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M372" s="2" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
@@ -22829,6 +23510,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M373" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
@@ -22889,6 +23575,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M374" s="2" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
@@ -22949,6 +23636,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M375" s="2" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
@@ -23009,6 +23697,7 @@
           <t>ja (Rot-Kandidat E2/E3)</t>
         </is>
       </c>
+      <c r="M376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
@@ -23069,6 +23758,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M377" s="2" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
@@ -23129,6 +23819,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M378" s="2" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
@@ -23189,6 +23880,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M379" s="2" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
@@ -23249,6 +23941,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M380" s="2" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
@@ -23309,6 +24002,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M381" s="2" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
@@ -23369,6 +24063,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M382" s="2" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
@@ -23429,6 +24124,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M383" s="2" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
@@ -23489,6 +24185,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
@@ -23549,6 +24246,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M385" s="2" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
@@ -23609,6 +24307,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
@@ -23669,6 +24368,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
@@ -23729,6 +24429,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
@@ -23789,6 +24490,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
@@ -23849,6 +24551,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
@@ -23909,6 +24612,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
@@ -23969,6 +24673,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -24029,6 +24734,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -24089,6 +24795,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M394" s="2" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
@@ -24149,6 +24856,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M395" s="2" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
@@ -24209,6 +24917,7 @@
           <t>nein (Rot-Kandidat E2/E3)</t>
         </is>
       </c>
+      <c r="M396" s="2" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -24269,6 +24978,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M397" s="2" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -24329,6 +25039,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -24385,6 +25096,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M399" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -24445,6 +25161,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M400" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
@@ -24505,6 +25226,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M401" s="2" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -24565,6 +25287,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M402" s="2" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
@@ -24625,6 +25348,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M403" s="2" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
@@ -24685,6 +25409,7 @@
           <t>ja (E1-Entscheidung)</t>
         </is>
       </c>
+      <c r="M404" s="2" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -24745,6 +25470,7 @@
           <t>nein (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M405" s="2" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
@@ -24805,6 +25531,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M406" s="2" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
@@ -24865,6 +25592,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M407" s="2" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -24925,6 +25653,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M408" s="2" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
@@ -24985,6 +25714,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M409" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -25045,6 +25779,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M410" s="2" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -25105,6 +25840,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M411" s="2" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
@@ -25165,6 +25901,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M412" s="2" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
@@ -25225,6 +25962,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M413" s="2" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
@@ -25285,6 +26023,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M414" s="2" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
@@ -25345,6 +26084,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M415" s="2" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -25405,6 +26145,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M416" s="2" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -25465,6 +26206,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M417" s="2" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
@@ -25525,6 +26267,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M418" s="2" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
@@ -25585,6 +26328,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M419" s="2" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
@@ -25645,6 +26389,7 @@
           <t>ja (Schwester Accurion)</t>
         </is>
       </c>
+      <c r="M420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
@@ -25705,6 +26450,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M421" s="2" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -25765,6 +26511,7 @@
           <t>ja (größte Restunsicherheit)</t>
         </is>
       </c>
+      <c r="M422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
@@ -25825,6 +26572,7 @@
           <t>ja (Rot-Kandidat E2)</t>
         </is>
       </c>
+      <c r="M423" s="2" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
@@ -25885,6 +26633,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M424" s="2" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
@@ -25945,6 +26694,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M425" s="2" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
@@ -26005,6 +26755,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M426" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
@@ -26065,6 +26820,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M427" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
@@ -26125,6 +26885,7 @@
           <t>ja (Rot-Kandidat E3)</t>
         </is>
       </c>
+      <c r="M428" s="2" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
@@ -26185,6 +26946,7 @@
           <t>ja (Rot-Kandidat E2/E3)</t>
         </is>
       </c>
+      <c r="M429" s="2" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
@@ -26245,6 +27007,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M430" s="2" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
@@ -26305,6 +27068,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M431" s="2" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
@@ -26365,6 +27129,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M432" s="2" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
@@ -26425,6 +27190,7 @@
           <t>ja (stärkster Grün-Kandidat)</t>
         </is>
       </c>
+      <c r="M433" s="2" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
@@ -26485,6 +27251,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M434" s="2" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -26545,6 +27312,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M435" s="2" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
@@ -26605,6 +27373,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M436" s="2" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
@@ -26665,6 +27434,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M437" s="2" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
@@ -26725,6 +27495,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M438" s="2" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
@@ -26785,6 +27556,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M439" s="2" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
@@ -26845,6 +27617,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M440" s="2" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
@@ -26905,6 +27678,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M441" s="2" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -26965,6 +27739,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M442" s="2" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
@@ -27025,6 +27800,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M443" s="2" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
@@ -27085,6 +27861,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M444" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
@@ -27145,6 +27926,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M445" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
@@ -27205,6 +27991,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M446" s="2" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
@@ -27265,6 +28052,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M447" s="2" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
@@ -27325,6 +28113,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M448" s="2" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
@@ -27385,6 +28174,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M449" s="2" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
@@ -27445,6 +28235,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M450" s="2" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -27505,6 +28296,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M451" s="2" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
@@ -27565,6 +28357,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M452" s="2" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
@@ -27625,6 +28418,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M453" s="2" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
@@ -27685,6 +28479,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
@@ -27745,6 +28540,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M455" s="2" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
@@ -27805,6 +28601,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M456" s="2" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
@@ -27865,6 +28662,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M457" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
@@ -27925,6 +28727,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M458" s="2" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
@@ -27985,6 +28788,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M459" s="2" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
@@ -28045,6 +28849,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M460" s="2" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
@@ -28105,6 +28910,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M461" s="2" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -28165,6 +28971,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M462" s="2" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
@@ -28225,6 +29032,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M463" s="2" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
@@ -28285,6 +29093,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M464" s="2" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
@@ -28345,6 +29154,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M465" s="2" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
@@ -28405,6 +29215,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M466" s="2" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
@@ -28465,6 +29276,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M467" s="2" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
@@ -28525,6 +29337,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M468" s="2" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
@@ -28585,6 +29398,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M469" s="2" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
@@ -28645,6 +29459,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M470" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
@@ -28705,6 +29524,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M471" s="2" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
@@ -28765,6 +29585,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
@@ -28825,6 +29646,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M473" s="2" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
@@ -28885,6 +29707,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M474" s="2" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
@@ -28945,6 +29768,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M475" s="2" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
@@ -29005,6 +29829,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M476" s="2" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
@@ -29065,6 +29890,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M477" s="2" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
@@ -29125,6 +29951,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M478" s="2" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
@@ -29185,6 +30012,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M479" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -29245,6 +30077,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M480" s="2" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
@@ -29305,6 +30138,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M481" s="2" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
@@ -29365,6 +30199,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M482" s="2" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
@@ -29425,6 +30260,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M483" s="2" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
@@ -29485,6 +30321,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M484" s="2" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
@@ -29545,6 +30382,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M485" s="2" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
@@ -29605,6 +30443,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M486" s="2" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
@@ -29665,6 +30504,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M487" s="2" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
@@ -29725,6 +30565,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M488" s="2" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
@@ -29785,6 +30626,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M489" s="2" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
@@ -29845,6 +30687,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M490" s="2" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
@@ -29905,6 +30748,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M491" s="2" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
@@ -29965,6 +30809,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M492" s="2" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
@@ -30025,6 +30870,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M493" s="2" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
@@ -30085,6 +30931,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M494" s="2" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
@@ -30145,6 +30992,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M495" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
@@ -30205,6 +31057,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M496" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
@@ -30265,6 +31122,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M497" s="2" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
@@ -30325,6 +31183,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M498" s="2" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
@@ -30385,6 +31244,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M499" s="2" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
@@ -30445,6 +31305,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M500" s="2" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
@@ -30505,6 +31366,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M501" s="2" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
@@ -30565,6 +31427,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M502" s="2" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
@@ -30625,6 +31488,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M503" s="2" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
@@ -30685,6 +31549,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M504" s="2" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
@@ -30745,6 +31610,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M505" s="2" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
@@ -30805,6 +31671,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M506" s="2" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
@@ -30865,6 +31732,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M507" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
@@ -30925,6 +31797,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M508" s="2" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
@@ -30985,6 +31858,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M509" s="2" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
@@ -31045,6 +31919,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M510" s="2" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
@@ -31105,6 +31980,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M511" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
@@ -31165,6 +32045,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M512" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
@@ -31225,6 +32110,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M513" s="2" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
@@ -31285,6 +32171,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M514" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
@@ -31345,6 +32236,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M515" s="2" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
@@ -31405,6 +32297,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M516" s="2" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
@@ -31465,6 +32358,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M517" s="2" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
@@ -31525,6 +32419,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M518" s="2" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
@@ -31585,6 +32480,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M519" s="2" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
@@ -31645,6 +32541,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M520" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
@@ -31705,6 +32606,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M521" s="2" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
@@ -31765,6 +32667,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M522" s="2" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
@@ -31825,6 +32728,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M523" s="2" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
@@ -31885,6 +32789,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M524" s="2" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
@@ -31945,6 +32850,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M525" s="2" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
@@ -32005,6 +32911,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M526" s="2" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
@@ -32065,6 +32972,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M527" s="2" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
@@ -32125,6 +33033,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M528" s="2" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
@@ -32185,6 +33094,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M529" s="2" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
@@ -32245,6 +33155,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M530" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
@@ -32305,6 +33220,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M531" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
@@ -32365,6 +33285,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M532" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
@@ -32425,6 +33350,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M533" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
@@ -32485,6 +33415,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M534" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
@@ -32545,6 +33480,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M535" s="2" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
@@ -32605,6 +33541,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M536" s="2" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
@@ -32665,6 +33602,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M537" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
@@ -32725,6 +33667,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M538" s="2" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
@@ -32785,6 +33728,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M539" s="2" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
@@ -32845,6 +33789,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M540" s="2" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
@@ -32905,6 +33850,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M541" s="2" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n">
@@ -32965,6 +33911,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M542" s="2" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n">
@@ -33025,6 +33972,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M543" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n">
@@ -33085,6 +34037,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M544" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
@@ -33145,6 +34102,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M545" s="2" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n">
@@ -33205,6 +34163,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M546" s="2" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
@@ -33265,6 +34224,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M547" s="2" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n">
@@ -33325,6 +34285,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M548" s="2" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n">
@@ -33385,6 +34346,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M549" s="2" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n">
@@ -33445,6 +34407,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M550" s="2" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n">
@@ -33505,6 +34468,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M551" s="2" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n">
@@ -33565,6 +34529,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M552" s="2" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
@@ -33625,6 +34590,7 @@
           <t>nein (siehe Nr. 3)</t>
         </is>
       </c>
+      <c r="M553" s="2" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
@@ -33685,6 +34651,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M554" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
@@ -33745,6 +34716,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M555" s="2" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
@@ -33805,6 +34777,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M556" s="2" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
@@ -33865,6 +34838,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M557" s="2" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
@@ -33925,6 +34899,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M558" s="2" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
@@ -33985,6 +34960,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M559" s="2" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
@@ -34045,6 +35021,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M560" s="2" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
@@ -34105,6 +35082,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M561" s="2" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
@@ -34165,6 +35143,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M562" s="2" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
@@ -34225,6 +35204,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M563" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
@@ -34285,6 +35269,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M564" s="2" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
@@ -34345,6 +35330,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M565" s="2" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
@@ -34405,6 +35391,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M566" s="2" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
@@ -34465,6 +35452,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M567" s="2" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
@@ -34525,6 +35513,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M568" s="2" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
@@ -34585,6 +35574,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M569" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n">
@@ -34645,6 +35639,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M570" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n">
@@ -34705,6 +35704,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M571" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
@@ -34765,6 +35769,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M572" s="2" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
@@ -34825,6 +35830,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M573" s="2" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
@@ -34885,6 +35891,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M574" s="2" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
@@ -34945,6 +35952,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M575" s="2" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
@@ -35005,6 +36013,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M576" s="2" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
@@ -35065,6 +36074,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M577" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
@@ -35125,6 +36139,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M578" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenbauer ohne Verguss-/Demak-Anlage – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
@@ -35185,6 +36204,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M579" s="2" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
@@ -35245,6 +36265,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M580" s="2" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
@@ -35305,6 +36326,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M581" s="2" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
@@ -35365,6 +36387,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M582" s="2" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
@@ -35425,6 +36448,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M583" s="2" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
@@ -35485,6 +36509,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M584" s="2" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
@@ -35545,6 +36570,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M585" s="2" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
@@ -35605,6 +36631,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
@@ -35665,6 +36692,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M587" s="2" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
@@ -35725,6 +36753,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
@@ -35785,6 +36814,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M589" s="2" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
@@ -35845,6 +36875,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M590" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
@@ -35905,6 +36940,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M591" s="2" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
@@ -35965,6 +37001,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M592" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
@@ -36025,6 +37066,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M593" s="2" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
@@ -36085,6 +37127,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
@@ -36145,6 +37188,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M595" s="2" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
@@ -36205,6 +37249,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M596" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
@@ -36265,6 +37314,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M597" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
@@ -36325,6 +37379,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M598" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
@@ -36385,6 +37444,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M599" s="2" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
@@ -36445,6 +37505,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
@@ -36505,6 +37566,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M601" s="2" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
@@ -36565,6 +37627,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
@@ -36625,6 +37688,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M603" s="2" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
@@ -36685,6 +37749,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
@@ -36745,6 +37810,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M605" s="2" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
@@ -36805,6 +37871,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
@@ -36865,6 +37932,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M607" s="2" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
@@ -36925,6 +37993,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M608" s="2" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
@@ -36981,6 +38050,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M609" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
@@ -37041,6 +38115,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M610" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
@@ -37101,6 +38180,7 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M611" s="2" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
@@ -37161,6 +38241,11 @@
           <t>nein</t>
         </is>
       </c>
+      <c r="M612" s="2" t="inlineStr">
+        <is>
+          <t>Verband / Prüfdienstleister / Forschung – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
@@ -37221,6 +38306,11 @@
           <t>ja (CRM-Ort bestätigen)</t>
         </is>
       </c>
+      <c r="M613" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
@@ -37277,6 +38367,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M614" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
@@ -37337,6 +38432,11 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M615" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
@@ -37397,9 +38497,14 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="M616" s="2" t="inlineStr">
+        <is>
+          <t>Im CRM (gleicher oder sehr ähnlicher Name) – laut Jey raus</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L616"/>
+  <autoFilter ref="A1:M616"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
